--- a/Backend/Input/Gestion riesgos/planilla_riesgos.xlsx
+++ b/Backend/Input/Gestion riesgos/planilla_riesgos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/Gestión de Riesgos/2024/Diciembre/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/Gestión de Riesgos/2025/Febrero/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{8DA4E4B1-C671-4E79-8AC4-F799C28A0995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E094DE2A-A12D-4D27-A40B-B0E203B114BF}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{8DA4E4B1-C671-4E79-8AC4-F799C28A0995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60ECB98A-2E9B-48F6-B715-692A6D64E944}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{7D582672-387C-43DA-B99F-6DF608B8FC7C}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7D582672-387C-43DA-B99F-6DF608B8FC7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Herramienta_Monitoreo" sheetId="1" r:id="rId1"/>
@@ -187,13 +187,13 @@
     <t>Impacto</t>
   </si>
   <si>
-    <t>Monitoreado 30/06</t>
-  </si>
-  <si>
     <t>Pendiente actualizar</t>
   </si>
   <si>
     <t xml:space="preserve">Actualizado </t>
+  </si>
+  <si>
+    <t>Se realizará monitoreo con corte al 31/03</t>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -776,9 +776,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -858,6 +855,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -900,17 +912,8 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1251,17 +1254,16 @@
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="39.140625" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="3" max="4" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1"/>
     <row r="3" spans="2:4" ht="18">
-      <c r="B3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
+      <c r="B3" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
     </row>
     <row r="4" spans="2:4" ht="30.75" thickBot="1">
       <c r="B4" s="1" t="s">
@@ -1278,10 +1280,10 @@
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="5">
         <v>2019</v>
       </c>
     </row>
@@ -1289,10 +1291,10 @@
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="8">
+      <c r="C6" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="6">
         <v>2024</v>
       </c>
     </row>
@@ -1300,10 +1302,10 @@
       <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="C7" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="6">
         <v>2024</v>
       </c>
     </row>
@@ -1311,21 +1313,21 @@
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="8">
+      <c r="C8" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="6">
         <v>2024</v>
       </c>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="8">
+      <c r="C9" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="6">
         <v>2024</v>
       </c>
     </row>
@@ -1333,10 +1335,10 @@
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="8">
+      <c r="C10" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="6">
         <v>2024</v>
       </c>
     </row>
@@ -1344,96 +1346,96 @@
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="C11" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="6">
         <v>2024</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="15.75" thickBot="1">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="C12" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="6">
         <v>2024</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="15.75" thickBot="1"/>
     <row r="14" spans="2:4" ht="18">
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
     </row>
     <row r="15" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="21.75" customHeight="1">
-      <c r="B16" s="14" t="s">
+    <row r="16" spans="2:4" ht="28.5" customHeight="1">
+      <c r="B16" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>16</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="21.75" customHeight="1">
-      <c r="B17" s="14" t="s">
+      <c r="D16" s="52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="28.5" customHeight="1">
+      <c r="B17" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="15">
-        <v>10</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="19.5" customHeight="1">
-      <c r="B18" s="14" t="s">
+      <c r="C17" s="14">
+        <v>13</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="30.75" customHeight="1">
+      <c r="B18" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="15">
-        <v>39</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="24" customHeight="1">
-      <c r="B19" s="14" t="s">
+      <c r="C18" s="14">
+        <v>35</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="27" customHeight="1">
+      <c r="B19" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="14">
+        <v>21</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="31.5" customHeight="1" thickBot="1">
+      <c r="B20" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="21" customHeight="1" thickBot="1">
-      <c r="B20" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="17">
-        <v>3</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>49</v>
+      <c r="C20" s="16">
+        <v>2</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1458,634 +1460,634 @@
   <sheetData>
     <row r="2" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="3" spans="2:9" ht="15.75">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
     </row>
     <row r="5" spans="2:9" ht="15" customHeight="1">
-      <c r="B5" s="45"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="26" t="s">
+      <c r="B5" s="49"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="19" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="18.75">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="34">
         <v>4</v>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="34">
         <v>8</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="34">
         <v>30</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="34">
         <v>53</v>
       </c>
-      <c r="G6" s="48">
-        <v>0</v>
-      </c>
-      <c r="H6" s="48">
+      <c r="G6" s="34">
+        <v>0</v>
+      </c>
+      <c r="H6" s="34">
         <v>8</v>
       </c>
-      <c r="I6" s="48">
+      <c r="I6" s="34">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="18.75">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="34">
         <v>11</v>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="34">
         <v>30</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="34">
         <v>105</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="34">
         <v>105</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="34">
         <v>8</v>
       </c>
-      <c r="H7" s="48">
-        <v>0</v>
-      </c>
-      <c r="I7" s="48">
+      <c r="H7" s="34">
+        <v>0</v>
+      </c>
+      <c r="I7" s="34">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="18.75">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="48">
+      <c r="C8" s="34">
         <v>19</v>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="34">
         <v>58</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="34">
         <v>99</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="34">
         <v>107</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="34">
         <v>8</v>
       </c>
-      <c r="H8" s="48">
+      <c r="H8" s="34">
         <v>6</v>
       </c>
-      <c r="I8" s="48">
+      <c r="I8" s="34">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="18.75">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="34">
         <v>15</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="34">
         <v>49</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="34">
         <v>127</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="34">
         <v>134</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="34">
         <v>12</v>
       </c>
-      <c r="H9" s="48">
+      <c r="H9" s="34">
         <v>5</v>
       </c>
-      <c r="I9" s="48">
+      <c r="I9" s="34">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="34">
         <v>1</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="34">
         <v>2</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="34">
         <v>4</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="34">
         <v>4</v>
       </c>
-      <c r="G10" s="48">
-        <v>0</v>
-      </c>
-      <c r="H10" s="48">
+      <c r="G10" s="34">
+        <v>0</v>
+      </c>
+      <c r="H10" s="34">
         <v>2</v>
       </c>
-      <c r="I10" s="48">
+      <c r="I10" s="34">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="34">
         <v>5</v>
       </c>
-      <c r="D11" s="48">
+      <c r="D11" s="34">
         <v>8</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="34">
         <v>22</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="34">
         <v>22</v>
       </c>
-      <c r="G11" s="48">
-        <v>0</v>
-      </c>
-      <c r="H11" s="48">
+      <c r="G11" s="34">
+        <v>0</v>
+      </c>
+      <c r="H11" s="34">
         <v>2</v>
       </c>
-      <c r="I11" s="48">
+      <c r="I11" s="34">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="18.75">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="34">
         <v>9</v>
       </c>
-      <c r="D12" s="48">
+      <c r="D12" s="34">
         <v>22</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="34">
         <v>32</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="34">
         <v>33</v>
       </c>
-      <c r="G12" s="48">
-        <v>0</v>
-      </c>
-      <c r="H12" s="48">
-        <v>0</v>
-      </c>
-      <c r="I12" s="48">
+      <c r="G12" s="34">
+        <v>0</v>
+      </c>
+      <c r="H12" s="34">
+        <v>0</v>
+      </c>
+      <c r="I12" s="34">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="18.75">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="34">
         <v>3</v>
       </c>
-      <c r="D13" s="48">
+      <c r="D13" s="34">
         <v>8</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="34">
         <v>50</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="34">
         <v>62</v>
       </c>
-      <c r="G13" s="48">
-        <v>0</v>
-      </c>
-      <c r="H13" s="48">
+      <c r="G13" s="34">
+        <v>0</v>
+      </c>
+      <c r="H13" s="34">
         <v>10</v>
       </c>
-      <c r="I13" s="48">
+      <c r="I13" s="34">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="34">
         <v>1</v>
       </c>
-      <c r="D14" s="48">
+      <c r="D14" s="34">
         <v>2</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="34">
         <v>4</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="34">
         <v>6</v>
       </c>
-      <c r="G14" s="48">
-        <v>0</v>
-      </c>
-      <c r="H14" s="48">
-        <v>0</v>
-      </c>
-      <c r="I14" s="48">
+      <c r="G14" s="34">
+        <v>0</v>
+      </c>
+      <c r="H14" s="34">
+        <v>0</v>
+      </c>
+      <c r="I14" s="34">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="21.75" thickBot="1">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="21">
         <f t="shared" ref="C15:I15" si="0">SUM(C6:C14)</f>
         <v>68</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <f t="shared" si="0"/>
         <v>187</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="22">
         <f t="shared" si="0"/>
         <v>473</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="22">
         <f t="shared" si="0"/>
         <v>526</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="22">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="22">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="21">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="18" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="43"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="47"/>
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1">
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="I19" s="21" t="s">
+      <c r="I19" s="20" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="27"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="21"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="20"/>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="49">
+      <c r="C21" s="35">
         <v>3</v>
       </c>
-      <c r="D21" s="50">
+      <c r="D21" s="36">
         <v>1</v>
       </c>
-      <c r="E21" s="49">
-        <v>0</v>
-      </c>
-      <c r="F21" s="50">
-        <v>0</v>
-      </c>
-      <c r="G21" s="49">
+      <c r="E21" s="35">
+        <v>0</v>
+      </c>
+      <c r="F21" s="36">
+        <v>0</v>
+      </c>
+      <c r="G21" s="35">
         <v>3</v>
       </c>
-      <c r="H21" s="50">
-        <v>0</v>
-      </c>
-      <c r="I21" s="51">
+      <c r="H21" s="36">
+        <v>0</v>
+      </c>
+      <c r="I21" s="37">
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="49">
-        <v>0</v>
-      </c>
-      <c r="D22" s="50">
-        <v>0</v>
-      </c>
-      <c r="E22" s="49">
+      <c r="C22" s="35">
+        <v>0</v>
+      </c>
+      <c r="D22" s="36">
+        <v>0</v>
+      </c>
+      <c r="E22" s="35">
         <v>9</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="36">
         <v>3</v>
       </c>
-      <c r="G22" s="49">
+      <c r="G22" s="35">
         <v>2</v>
       </c>
-      <c r="H22" s="50">
+      <c r="H22" s="36">
         <v>1</v>
       </c>
-      <c r="I22" s="51">
+      <c r="I22" s="37">
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="49">
+      <c r="C23" s="35">
         <v>1</v>
       </c>
-      <c r="D23" s="50">
-        <v>0</v>
-      </c>
-      <c r="E23" s="49">
+      <c r="D23" s="36">
+        <v>0</v>
+      </c>
+      <c r="E23" s="35">
         <v>3</v>
       </c>
-      <c r="F23" s="50">
+      <c r="F23" s="36">
         <v>4</v>
       </c>
-      <c r="G23" s="49">
+      <c r="G23" s="35">
         <v>2</v>
       </c>
-      <c r="H23" s="50">
-        <v>0</v>
-      </c>
-      <c r="I23" s="51">
+      <c r="H23" s="36">
+        <v>0</v>
+      </c>
+      <c r="I23" s="37">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="49">
+      <c r="C24" s="35">
         <v>2</v>
       </c>
-      <c r="D24" s="50">
-        <v>0</v>
-      </c>
-      <c r="E24" s="49">
+      <c r="D24" s="36">
+        <v>0</v>
+      </c>
+      <c r="E24" s="35">
         <v>4</v>
       </c>
-      <c r="F24" s="50">
+      <c r="F24" s="36">
         <v>2</v>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="35">
         <v>9</v>
       </c>
-      <c r="H24" s="50">
+      <c r="H24" s="36">
         <v>2</v>
       </c>
-      <c r="I24" s="51">
+      <c r="I24" s="37">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="49">
+      <c r="C25" s="35">
         <v>2</v>
       </c>
-      <c r="D25" s="50">
+      <c r="D25" s="36">
         <v>2</v>
       </c>
-      <c r="E25" s="49">
-        <v>0</v>
-      </c>
-      <c r="F25" s="50">
-        <v>0</v>
-      </c>
-      <c r="G25" s="49">
+      <c r="E25" s="35">
+        <v>0</v>
+      </c>
+      <c r="F25" s="36">
+        <v>0</v>
+      </c>
+      <c r="G25" s="35">
         <v>1</v>
       </c>
-      <c r="H25" s="50">
+      <c r="H25" s="36">
         <v>1</v>
       </c>
-      <c r="I25" s="51">
+      <c r="I25" s="37">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="49">
+      <c r="C26" s="35">
         <v>1</v>
       </c>
-      <c r="D26" s="50">
-        <v>0</v>
-      </c>
-      <c r="E26" s="49">
-        <v>0</v>
-      </c>
-      <c r="F26" s="50">
-        <v>0</v>
-      </c>
-      <c r="G26" s="49">
+      <c r="D26" s="36">
+        <v>0</v>
+      </c>
+      <c r="E26" s="35">
+        <v>0</v>
+      </c>
+      <c r="F26" s="36">
+        <v>0</v>
+      </c>
+      <c r="G26" s="35">
         <v>4</v>
       </c>
-      <c r="H26" s="50">
-        <v>0</v>
-      </c>
-      <c r="I26" s="51">
+      <c r="H26" s="36">
+        <v>0</v>
+      </c>
+      <c r="I26" s="37">
         <v>5</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="49">
-        <v>0</v>
-      </c>
-      <c r="D27" s="50">
-        <v>0</v>
-      </c>
-      <c r="E27" s="49">
-        <v>0</v>
-      </c>
-      <c r="F27" s="50">
-        <v>0</v>
-      </c>
-      <c r="G27" s="49">
+      <c r="C27" s="35">
+        <v>0</v>
+      </c>
+      <c r="D27" s="36">
+        <v>0</v>
+      </c>
+      <c r="E27" s="35">
+        <v>0</v>
+      </c>
+      <c r="F27" s="36">
+        <v>0</v>
+      </c>
+      <c r="G27" s="35">
         <v>5</v>
       </c>
-      <c r="H27" s="50">
-        <v>0</v>
-      </c>
-      <c r="I27" s="51">
+      <c r="H27" s="36">
+        <v>0</v>
+      </c>
+      <c r="I27" s="37">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="49">
+      <c r="C28" s="35">
         <v>4</v>
       </c>
-      <c r="D28" s="50">
+      <c r="D28" s="36">
         <v>1</v>
       </c>
-      <c r="E28" s="49">
-        <v>0</v>
-      </c>
-      <c r="F28" s="50">
-        <v>0</v>
-      </c>
-      <c r="G28" s="49">
+      <c r="E28" s="35">
+        <v>0</v>
+      </c>
+      <c r="F28" s="36">
+        <v>0</v>
+      </c>
+      <c r="G28" s="35">
         <v>6</v>
       </c>
-      <c r="H28" s="50">
+      <c r="H28" s="36">
         <v>1</v>
       </c>
-      <c r="I28" s="51">
+      <c r="I28" s="37">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="49">
-        <v>0</v>
-      </c>
-      <c r="D29" s="50">
-        <v>0</v>
-      </c>
-      <c r="E29" s="49">
-        <v>0</v>
-      </c>
-      <c r="F29" s="50">
-        <v>0</v>
-      </c>
-      <c r="G29" s="49">
+      <c r="C29" s="35">
+        <v>0</v>
+      </c>
+      <c r="D29" s="36">
+        <v>0</v>
+      </c>
+      <c r="E29" s="35">
+        <v>0</v>
+      </c>
+      <c r="F29" s="36">
+        <v>0</v>
+      </c>
+      <c r="G29" s="35">
         <v>3</v>
       </c>
-      <c r="H29" s="50">
+      <c r="H29" s="36">
         <v>3</v>
       </c>
-      <c r="I29" s="51">
+      <c r="I29" s="37">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="2:9" ht="19.5" thickBot="1">
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="28">
         <f t="shared" ref="C30:I30" si="1">SUM(C21:C29)</f>
         <v>13</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="28">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="28">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="28">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="28">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="18">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
@@ -2113,288 +2115,288 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="30" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:4">
-      <c r="B4" s="32">
+      <c r="B4" s="31">
         <v>1</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="31">
         <v>1</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="32">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="32">
+      <c r="B5" s="31">
         <v>2</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="31">
         <v>1</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="32">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="32">
+      <c r="B6" s="31">
         <v>3</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="31">
         <v>1</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="32">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="32">
+      <c r="B7" s="31">
         <v>4</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="31">
         <v>1</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="32">
+      <c r="B8" s="31">
         <v>5</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="31">
         <v>1</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="32">
+      <c r="B9" s="31">
         <v>1</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="31">
         <v>2</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="32">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="32">
+      <c r="B10" s="31">
         <v>2</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="31">
         <v>2</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="32">
         <v>55</v>
       </c>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="32">
+      <c r="B11" s="31">
         <v>3</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="31">
         <v>2</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="32">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="32">
+      <c r="B12" s="31">
         <v>4</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="31">
         <v>2</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="32">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="32">
+      <c r="B13" s="31">
         <v>5</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="31">
         <v>2</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="32">
+      <c r="B14" s="31">
         <v>1</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="31">
         <v>3</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="32">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="32">
+      <c r="B15" s="31">
         <v>2</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="31">
         <v>3</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="32">
         <v>72</v>
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="32">
+      <c r="B16" s="31">
         <v>3</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="31">
         <v>3</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="32">
         <v>96</v>
       </c>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="32">
+      <c r="B17" s="31">
         <v>4</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="31">
         <v>3</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="32">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="32">
+      <c r="B18" s="31">
         <v>5</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="31">
         <v>3</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="32">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="32">
+      <c r="B19" s="31">
         <v>1</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="31">
         <v>4</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="32">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="32">
+      <c r="B20" s="31">
         <v>2</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="31">
         <v>4</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="32">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:4">
-      <c r="B21" s="32">
+      <c r="B21" s="31">
         <v>3</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="31">
         <v>4</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="32">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="2:4">
-      <c r="B22" s="32">
+      <c r="B22" s="31">
         <v>4</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="31">
         <v>4</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="32">
         <v>18</v>
       </c>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="32">
+      <c r="B23" s="31">
         <v>5</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="31">
         <v>4</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:4">
-      <c r="B24" s="32">
+      <c r="B24" s="31">
         <v>1</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="31">
         <v>5</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="32">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="32">
+      <c r="B25" s="31">
         <v>2</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="31">
         <v>5</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="32">
         <v>10</v>
       </c>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="32">
+      <c r="B26" s="31">
         <v>3</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="31">
         <v>5</v>
       </c>
-      <c r="D26" s="33">
+      <c r="D26" s="32">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="32">
+      <c r="B27" s="31">
         <v>4</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="31">
         <v>5</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:4">
-      <c r="B28" s="32">
+      <c r="B28" s="31">
         <v>5</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="31">
         <v>5</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="32">
         <v>0</v>
       </c>
     </row>
@@ -2404,8 +2406,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="22" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="c12b387725171b57bce8d20228431399">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0b67a6e2ff3c9ebaa3c6cdc8923b4bdc" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="22" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="99316247900046118e13a249c2e2a979">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18ff31ee8df8f768b70ea272e17d0ebc" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
     <xsd:import namespace="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
     <xsd:element name="properties">
@@ -2431,7 +2454,7 @@
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:orden"/>
+                <xsd:element ref="ns2:orden" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2518,7 +2541,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="orden" ma:index="26" ma:displayName="orden" ma:format="Dropdown" ma:internalName="orden" ma:percentage="FALSE">
+    <xsd:element name="orden" ma:index="26" nillable="true" ma:displayName="orden" ma:format="Dropdown" ma:internalName="orden" ma:percentage="FALSE">
       <xsd:simpleType>
         <xsd:restriction base="dms:Number">
           <xsd:maxInclusive value="12"/>
@@ -2667,29 +2690,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7763FF1-A5DD-4BF6-9D22-67DE12C34045}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18A04A5F-AA73-4640-9A45-FA0463B4A2FA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2701,12 +2710,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18A04A5F-AA73-4640-9A45-FA0463B4A2FA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8ED488C-2573-49DB-8E1B-F5CFCC329B05}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
     <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>